--- a/data/supplementary_tables/Supplementary Table 13.xlsx
+++ b/data/supplementary_tables/Supplementary Table 13.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Eukaryotes_Asgard_TACK/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_verified_red/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C482A5E-0D33-A044-A7B2-8F0D7A51269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDECA3BC-EC3E-4E4E-BB43-EEE7C6F7A353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="606">
   <si>
     <t>ESP_ID</t>
   </si>
@@ -38,12 +38,12 @@
     <t>Protein_Description</t>
   </si>
   <si>
+    <t>Protein_Short_Name</t>
+  </si>
+  <si>
     <t>ESP_Category</t>
   </si>
   <si>
-    <t>Experimental_Evidence_Level</t>
-  </si>
-  <si>
     <t>Evidence_Type</t>
   </si>
   <si>
@@ -62,16 +62,13 @@
     <t>Evidence_Annotation_Notes</t>
   </si>
   <si>
-    <t>Protein_Short_Name</t>
-  </si>
-  <si>
     <t>Thor__B59_G1__03300</t>
   </si>
   <si>
     <t>ATPase which is responsible for recognizing, binding, unfolding and translocation of substrate proteins into the archaeal 20S proteasome core particle. Is essential for opening the gate of the 20S proteasome via an interaction with its C- terminus, thereby allowing substrate entry and access to the site of proteolysis. Thus, the C-termini of the proteasomal ATPase function like a 'key in a lock' to induce gate opening and therefore regulate proteolysis. Unfolding activity requires energy from ATP hydrolysis, whereas ATP binding alone promotes ATPase-20S proteasome association which triggers gate opening, and supports translocation of unfolded substrates</t>
   </si>
   <si>
-    <t>Cellular processes and signaling</t>
+    <t>Proteasomal ATPase</t>
   </si>
   <si>
     <t>L3</t>
@@ -95,15 +92,15 @@
     <t>The archaeal PAN/20S proteasome has gating, structural, and biochemical experiments; no direct experiment has been found for the DPANN homologs, so this is conservatively assigned as L3.</t>
   </si>
   <si>
-    <t>Proteasomal ATPase</t>
-  </si>
-  <si>
     <t>cog.007997</t>
   </si>
   <si>
     <t>polypeptide N-acetylgalactosaminyltransferase 6</t>
   </si>
   <si>
+    <t>ppGalNAc-T6</t>
+  </si>
+  <si>
     <t>Multiple</t>
   </si>
   <si>
@@ -116,9 +113,6 @@
     <t>No direct within-DPANN experiment or traceable family-level experimental literature was found; retained only as a homology/functional-annotation candidate.</t>
   </si>
   <si>
-    <t>ppGalNAc-T6</t>
-  </si>
-  <si>
     <t>Thor__M8_58_Bin_135__00104</t>
   </si>
   <si>
@@ -137,9 +131,6 @@
     <t>Thor__D4993_C5_LG_Bin_146__00087</t>
   </si>
   <si>
-    <t>eIF-2 functions in the early steps of protein synthesis by forming a ternary complex with GTP and initiator tRNA</t>
-  </si>
-  <si>
     <t>Information storage and processing</t>
   </si>
   <si>
@@ -152,9 +143,6 @@
     <t>Verified as structural evidence for the complete archaeal translation-initiation factor aIF2 complex; used as family-level support.</t>
   </si>
   <si>
-    <t>Eif-2</t>
-  </si>
-  <si>
     <t>HeHe__S2_bin51__00313</t>
   </si>
   <si>
@@ -179,12 +167,12 @@
     <t>Phenylalanine-4-hydroxylase</t>
   </si>
   <si>
+    <t>Phe-4-hydroxylase</t>
+  </si>
+  <si>
     <t>Metabolism</t>
   </si>
   <si>
-    <t>Phe-4-hydroxylase</t>
-  </si>
-  <si>
     <t>HeHo__M3_44_Bin_131__05223</t>
   </si>
   <si>
@@ -227,6 +215,9 @@
     <t>Belongs to the MCM family</t>
   </si>
   <si>
+    <t>MCM family</t>
+  </si>
+  <si>
     <t>Euryarchaeota</t>
   </si>
   <si>
@@ -242,18 +233,12 @@
     <t>MCM helicase has structural, biochemical, and ATPase/helicase-related experiments in other archaea; no direct experiment is available for the DPANN homologs.</t>
   </si>
   <si>
-    <t>MCM family</t>
-  </si>
-  <si>
     <t>cog.014349</t>
   </si>
   <si>
     <t>Catalyzes the hydrolysis of the N-glycosidic bond in the first two intermediates of riboflavin biosynthesis, which are highly reactive metabolites, yielding relatively innocuous products. Thus, can divert a surplus of harmful intermediates into relatively harmless products and pre-empt the damage these intermediates would otherwise do. Helps maintain flavin levels. May act on other substrates in vivo. Has no activity against GTP, nucleoside monophosphates or ADP-ribose. Is Required for swarming motility</t>
   </si>
   <si>
-    <t>Catalyzes the hydrolysis of the</t>
-  </si>
-  <si>
     <t>cog.011026</t>
   </si>
   <si>
@@ -293,6 +278,9 @@
     <t>Belongs to the eukaryotic ribosomal protein eS28 family</t>
   </si>
   <si>
+    <t>Eukaryotic Ribosomal Protein Es28 Family</t>
+  </si>
+  <si>
     <t>L2</t>
   </si>
   <si>
@@ -302,9 +290,6 @@
     <t>These entries are mainly ribosomal-protein homology annotations and are not treated as DPANN-specific ESP experimental evidence.</t>
   </si>
   <si>
-    <t>Eukaryotic Ribosomal Protein Es28 Family</t>
-  </si>
-  <si>
     <t>cog.000761</t>
   </si>
   <si>
@@ -341,9 +326,6 @@
     <t>cog.001012</t>
   </si>
   <si>
-    <t>Function in general translation initiation by promoting the binding of the formylmethionine-tRNA to ribosomes. Seems to function along with eIF-2</t>
-  </si>
-  <si>
     <t>Function in general translation initiation</t>
   </si>
   <si>
@@ -353,15 +335,15 @@
     <t>Binds to 23S rRNA. One of the proteins that surrounds the polypeptide exit tunnel on the outside of the ribosome</t>
   </si>
   <si>
-    <t>Binds to 23S rRNA.</t>
-  </si>
-  <si>
     <t>cog.000437</t>
   </si>
   <si>
     <t>Sliding clamp subunit that acts as a moving platform for DNA processing. Responsible for tethering the catalytic subunit of DNA polymerase and other proteins to DNA during high-speed replication</t>
   </si>
   <si>
+    <t>Sliding clamp subunit</t>
+  </si>
+  <si>
     <t>Pyrococcus furiosus</t>
   </si>
   <si>
@@ -374,9 +356,6 @@
     <t>Verified as crystal-structure evidence for the archaeal PCNA sliding clamp; the original table had mistakenly listed DOI 10.1110/ps.35701, which has now been corrected.</t>
   </si>
   <si>
-    <t>Sliding clamp subunit</t>
-  </si>
-  <si>
     <t>cog.004287</t>
   </si>
   <si>
@@ -386,6 +365,9 @@
     <t>DNA-dependent RNA polymerase catalyzes the transcription of DNA into RNA using the four ribonucleoside triphosphates as substrates</t>
   </si>
   <si>
+    <t>DNA-dependent RNA polymerase</t>
+  </si>
+  <si>
     <t>Experimental structural/transcription evidence from other archaea</t>
   </si>
   <si>
@@ -404,9 +386,6 @@
     <t>Archaeal RNA polymerase/general transcription machinery has structural experiments; no direct experiment has yet been found for the DPANN-derived entries.</t>
   </si>
   <si>
-    <t>DNA-dependent RNA polymerase</t>
-  </si>
-  <si>
     <t>cog.010784</t>
   </si>
   <si>
@@ -461,36 +440,24 @@
     <t>Large family of predicted nucleotide-binding domains</t>
   </si>
   <si>
-    <t>Large family of predicted...</t>
-  </si>
-  <si>
     <t>cog.005008</t>
   </si>
   <si>
     <t>Catalytic component of the COMPASS (Set1C) complex that specifically mono-, di- and trimethylates histone H3 to form H3K4me1 2 3, which subsequently plays a role in telomere length maintenance and transcription elongation regulation</t>
   </si>
   <si>
-    <t>COMPASS (Set1C) complex that specifically</t>
-  </si>
-  <si>
     <t>cog.001544</t>
   </si>
   <si>
     <t>Binds 16S rRNA, required for the assembly of 30S particles</t>
   </si>
   <si>
-    <t>Binds 16S rRNA</t>
-  </si>
-  <si>
     <t>cog.001283</t>
   </si>
   <si>
     <t>Catalyzes the last two sequential reactions in the de novo biosynthetic pathway for UDP-N-acetylglucosamine (UDP- GlcNAc). The C-terminal domain catalyzes the transfer of acetyl group from acetyl coenzyme A to glucosamine-1-phosphate (GlcN-1-P) to produce N-acetylglucosamine-1-phosphate (GlcNAc-1-P), which is converted into UDP-GlcNAc by the transfer of uridine 5- monophosphate (from uridine 5-triphosphate), a reaction catalyzed by the N-terminal domain</t>
   </si>
   <si>
-    <t>Catalyzes the last two sequential</t>
-  </si>
-  <si>
     <t>cog.000314</t>
   </si>
   <si>
@@ -506,6 +473,9 @@
     <t>Part of ribonuclease P, a protein complex that generates mature tRNA molecules by cleaving their 5'-ends</t>
   </si>
   <si>
+    <t>Part of ribonuclease P, a protein complex</t>
+  </si>
+  <si>
     <t>L5</t>
   </si>
   <si>
@@ -527,9 +497,6 @@
     <t>RNA-seq in Nanoarchaeum equitans validated processing of tRNA, CRISPR RNA, and related molecules; if the entry belongs to the corresponding RNA-processing system, this can serve as within-DPANN evidence.</t>
   </si>
   <si>
-    <t>Part of ribonuclease P, a protein complex</t>
-  </si>
-  <si>
     <t>cog.000075</t>
   </si>
   <si>
@@ -563,15 +530,15 @@
     <t>metal-dependent protease of the PAD1 JAB1 superfamily</t>
   </si>
   <si>
+    <t>Metal-dependent Protease of the PAD1</t>
+  </si>
+  <si>
     <t>Inference from domain-level homology</t>
   </si>
   <si>
     <t>The JAB/MPN domain suggests deubiquitinase/metalloprotease-related homology, but no direct experiment has been found within DPANN and the exact substrate/function remains unclear.</t>
   </si>
   <si>
-    <t>Metal-dependent Protease of the PAD1</t>
-  </si>
-  <si>
     <t>cog.001169</t>
   </si>
   <si>
@@ -602,18 +569,12 @@
     <t>subunit of the gamma-secretase complex, an endoprotease complex that catalyzes the intramembrane cleavage of integral membrane proteins such as Notch receptors</t>
   </si>
   <si>
-    <t>Gamma-secretase Complex, An Endoprotease...</t>
-  </si>
-  <si>
     <t>cog.001740</t>
   </si>
   <si>
     <t>Probable Brix domain-containing ribosomal biogenesis protein</t>
   </si>
   <si>
-    <t>Probable Brix domain-containing ribosomal...</t>
-  </si>
-  <si>
     <t>cog.000606</t>
   </si>
   <si>
@@ -656,9 +617,6 @@
     <t>Predicted SAM-dependent RNA methyltransferase</t>
   </si>
   <si>
-    <t>Predicted SAM-dependent RNA...</t>
-  </si>
-  <si>
     <t>cog.002654</t>
   </si>
   <si>
@@ -680,18 +638,12 @@
     <t>Could be responsible for synthesis of pseudouridine from uracil-13 in transfer RNAs</t>
   </si>
   <si>
-    <t>Could be</t>
-  </si>
-  <si>
     <t>cog.000943</t>
   </si>
   <si>
     <t>Dual specificity protein phosphatase, N-terminal half</t>
   </si>
   <si>
-    <t>Dual specificity protein phosphatase,...</t>
-  </si>
-  <si>
     <t>cog.001089</t>
   </si>
   <si>
@@ -746,9 +698,6 @@
     <t>Uptake of acetate and succinate. Transport is energetically dependent on the protonmotive force</t>
   </si>
   <si>
-    <t>Uptake of acetate and succinate.</t>
-  </si>
-  <si>
     <t>cog.011131</t>
   </si>
   <si>
@@ -773,9 +722,6 @@
     <t>Belongs to the mannose-6-phosphate isomerase type 2 family</t>
   </si>
   <si>
-    <t>Mannose-6-phosphate Isomerase Type 2...</t>
-  </si>
-  <si>
     <t>cog.008699</t>
   </si>
   <si>
@@ -791,6 +737,9 @@
     <t>Non-catalytic component of the exosome, which is a complex involved in RNA degradation. Increases the RNA binding and the efficiency of RNA degradation. Helpful for the interaction of the exosome with A-poor RNAs</t>
   </si>
   <si>
+    <t>Non-catalytic component of the exosome</t>
+  </si>
+  <si>
     <t>Lorentzen et al., 2005, Nature Structural &amp; Molecular Biology</t>
   </si>
   <si>
@@ -800,9 +749,6 @@
     <t>The Sulfolobus exosome core complex has crystal-structure and active-site mutational/biochemical evidence; no direct experiment has been found in DPANN.</t>
   </si>
   <si>
-    <t>Non-catalytic component of the exosome</t>
-  </si>
-  <si>
     <t>cog.000373</t>
   </si>
   <si>
@@ -824,9 +770,6 @@
     <t>Catalyzes the reversible transfer of the terminal phosphate group between ATP and AMP. Plays an important role in cellular energy homeostasis and in adenine nucleotide metabolism</t>
   </si>
   <si>
-    <t>Catalyzes the reversible transfer of</t>
-  </si>
-  <si>
     <t>cog.007221</t>
   </si>
   <si>
@@ -842,9 +785,6 @@
     <t>Binds directly to 23S rRNA. Probably involved in E site tRNA release</t>
   </si>
   <si>
-    <t>Binds directly to 23S rRNA.</t>
-  </si>
-  <si>
     <t>cog.000794</t>
   </si>
   <si>
@@ -929,9 +869,6 @@
     <t>protein N-acetylglucosaminyltransferase activity</t>
   </si>
   <si>
-    <t>Protein N-acetylglucosaminyltransferase...</t>
-  </si>
-  <si>
     <t>cog.001331</t>
   </si>
   <si>
@@ -986,9 +923,6 @@
     <t>Catalyzes the GTP-dependent ribosomal translocation step during translation elongation. During this step, the ribosome changes from the pre-translocational (PRE) to the post- translocational (POST) state as the newly formed A-site-bound peptidyl-tRNA and P-site-bound deacylated tRNA move to the P and E sites, respectively. Catalyzes the coordinated movement of the two tRNA molecules, the mRNA and conformational changes in the ribosome</t>
   </si>
   <si>
-    <t>Catalyzes the GTP-dependent ribosomal...</t>
-  </si>
-  <si>
     <t>cog.007547</t>
   </si>
   <si>
@@ -1025,6 +959,9 @@
     <t>Endonuclease that removes tRNA introns. Cleaves pre-tRNA at the 5'- and 3'-splice sites to release the intron. The products are an intron and two tRNA half-molecules bearing 2',3' cyclic phosphate and 5'-OH termini. Recognizes a pseudosymmetric substrate in which 2 bulged loops of 3 bases are separated by a stem of 4 bp</t>
   </si>
   <si>
+    <t>Endonuclease</t>
+  </si>
+  <si>
     <t>L4</t>
   </si>
   <si>
@@ -1040,9 +977,6 @@
     <t>The Nanoarchaeum equitans tRNA-splicing endonuclease has crystal-structure and functional assembly/substrate-cleavage experiments; this counts as direct protein-level evidence within DPANN.</t>
   </si>
   <si>
-    <t>Endonuclease</t>
-  </si>
-  <si>
     <t>cog.000921</t>
   </si>
   <si>
@@ -1067,9 +1001,6 @@
     <t>S-adenosyl-L-methionine-dependent methyltransferase that catalyzes the trimethylation of the amino group of the modified target histidine residue in translation elongation factor 2 (EF- 2), to form an intermediate called diphthine. The three successive methylation reactions represent the second step of diphthamide biosynthesis</t>
   </si>
   <si>
-    <t>S-adenosyl-L-methionine-dependent...</t>
-  </si>
-  <si>
     <t>cog.001992</t>
   </si>
   <si>
@@ -1106,9 +1037,6 @@
     <t>Catalyzes the ATP-dependent phosphorylation of the 3- deoxy-D-manno-octulosonic acid (Kdo) residue in Kdo-lipid IV(A) at the 4-OH position</t>
   </si>
   <si>
-    <t>Catalyzes the ATP-dependent...</t>
-  </si>
-  <si>
     <t>cog.000476</t>
   </si>
   <si>
@@ -1193,12 +1121,12 @@
     <t>Roadblock/LC7 domain</t>
   </si>
   <si>
+    <t>Roadblock/LC7</t>
+  </si>
+  <si>
     <t>Roadblock/LC7 supports only domain-homology inference; no direct experiment has been found within DPANN.</t>
   </si>
   <si>
-    <t>Roadblock/LC7</t>
-  </si>
-  <si>
     <t>Herm__H02S_Hermod_26__01615</t>
   </si>
   <si>
@@ -1238,9 +1166,6 @@
     <t>It is involved in the biological process described with cell adhesion</t>
   </si>
   <si>
-    <t>It is</t>
-  </si>
-  <si>
     <t>cog.001875</t>
   </si>
   <si>
@@ -1262,9 +1187,6 @@
     <t>The Sulfolobus ESCRT/Cdv system has cell-division, localization, and reconstitution evidence; no direct experiment is available for the corresponding DPANN entries.</t>
   </si>
   <si>
-    <t>Vacuolar protein sorting-associated...</t>
-  </si>
-  <si>
     <t>cog.001104</t>
   </si>
   <si>
@@ -1289,6 +1211,9 @@
     <t>Forms part of the ribosomal stalk which helps the ribosome interact with GTP-bound translation factors</t>
   </si>
   <si>
+    <t>Ribosomal stalk protein</t>
+  </si>
+  <si>
     <t>cog.012445</t>
   </si>
   <si>
@@ -1319,9 +1244,6 @@
     <t>Fibronectin type III domain-containing protein 2</t>
   </si>
   <si>
-    <t>Fibronectin type III domain-containing...</t>
-  </si>
-  <si>
     <t>cog.000841</t>
   </si>
   <si>
@@ -1448,9 +1370,6 @@
     <t>Belongs to the sodium neurotransmitter symporter (SNF) (TC 2.A.22) family</t>
   </si>
   <si>
-    <t>Sodium Neurotransmitter Symporter (snf)...</t>
-  </si>
-  <si>
     <t>HeHe__RS_8_8__01282</t>
   </si>
   <si>
@@ -1505,6 +1424,9 @@
     <t>ATP-dependent DNA helicase involved in DNA damage repair by homologous recombination and in genome maintenance. Capable of unwinding D-loops. Plays a role in limiting crossover recombinants during mitotic DNA double-strand break (DSB) repair. Component of a FANCM-MHF complex which promotes gene conversion at blocked replication forks, probably by reversal of the stalled fork</t>
   </si>
   <si>
+    <t>ATP-dependent DNA helicase</t>
+  </si>
+  <si>
     <t>Experimental structural evidence from other archaea for DNA repair</t>
   </si>
   <si>
@@ -1517,9 +1439,6 @@
     <t>Verified as structural and mutational-analysis literature for archaeal RadA (a Rad51 homolog); used to support homologous-recombination families.</t>
   </si>
   <si>
-    <t>ATP-dependent DNA helicase</t>
-  </si>
-  <si>
     <t>cog.002187</t>
   </si>
   <si>
@@ -1583,9 +1502,6 @@
     <t>methenyltetrahydrofolate synthetase domain containing</t>
   </si>
   <si>
-    <t>Methenyltetrahydrofolate Synthetase...</t>
-  </si>
-  <si>
     <t>cog.001039</t>
   </si>
   <si>
@@ -1613,9 +1529,6 @@
     <t>Verified as direct biochemical and structural literature for the archaeal FEN1/5'-exonuclease family.</t>
   </si>
   <si>
-    <t>Structure-specific nuclease with 5'-flap...</t>
-  </si>
-  <si>
     <t>cog.000742</t>
   </si>
   <si>
@@ -1640,9 +1553,6 @@
     <t>Stabilizes TBP binding to an archaeal box-A promoter. Also responsible for recruiting RNA polymerase II to the pre- initiation complex (DNA-TBP-TFIIB)</t>
   </si>
   <si>
-    <t>Stabilizes TBP binding to an</t>
-  </si>
-  <si>
     <t>Hela__Hel_GB_A__01083__267-546</t>
   </si>
   <si>
@@ -1799,17 +1709,143 @@
     <t>NA; Uncharacterised; hypothetical; -</t>
   </si>
   <si>
-    <t>Ribosomal stalk protein</t>
-  </si>
-  <si>
-    <t>Supplementary Table 13 | ESPs identified in DPANN archaea before and after genome decontamination, with genome counts, functional annotations and experimental evidence levels</t>
+    <t>Supplementary Table 13 | ESPs identified in DPANN archaea before and after genome decontamination, with genome counts, functional annotations and literature evidence levels</t>
+  </si>
+  <si>
+    <t>Evidence-level interpretation</t>
+  </si>
+  <si>
+    <t>Evidence levels annotate family-level literature support and were not used for ESP calling or contamination-sensitive counts.</t>
+  </si>
+  <si>
+    <t>Sequence or functional annotation only.</t>
+  </si>
+  <si>
+    <t>Domain or structural homology.</t>
+  </si>
+  <si>
+    <t>Experimental support from another archaeal lineage.</t>
+  </si>
+  <si>
+    <t>Direct biochemical or structural evidence for a focal-lineage homologue.</t>
+  </si>
+  <si>
+    <t>Within-lineage functional, localization or cellular evidence.</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Family-level evidence does not imply experimental validation of every sequence entry.</t>
+  </si>
+  <si>
+    <t>Nucleotide-binding domain protein</t>
+  </si>
+  <si>
+    <t>γ-secretase subunit</t>
+  </si>
+  <si>
+    <t>Brix domain-containing ribosome biogenesis protein</t>
+  </si>
+  <si>
+    <t>SAM-dependent RNA methyltransferase</t>
+  </si>
+  <si>
+    <t>Dual-specificity phosphatase</t>
+  </si>
+  <si>
+    <t>Mannose-6-phosphate isomerase</t>
+  </si>
+  <si>
+    <t>HAD hydrolase</t>
+  </si>
+  <si>
+    <t>Protein GlcNAc transferase activity</t>
+  </si>
+  <si>
+    <t>Catalyzes GTP-dependent ribosomal translocation during translation elongation</t>
+  </si>
+  <si>
+    <t>Diphthine synthase</t>
+  </si>
+  <si>
+    <t>TYW3</t>
+  </si>
+  <si>
+    <t>Catalyzes ATP-dependent 4-O phosphorylation of Kdo-lipid IV(A)</t>
+  </si>
+  <si>
+    <t>VPS-associated protein</t>
+  </si>
+  <si>
+    <t>FNIII domain-containing protein 2</t>
+  </si>
+  <si>
+    <t>SNF family transporter</t>
+  </si>
+  <si>
+    <t>MTHFS</t>
+  </si>
+  <si>
+    <t>5′-flap endonuclease involved in DNA replication and repair</t>
+  </si>
+  <si>
+    <t>Hydrolyzes reactive intermediates of riboflavin biosynthesis</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L24</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L14</t>
+  </si>
+  <si>
+    <t>Ribosomal protein S4</t>
+  </si>
+  <si>
+    <t>Catalytic subunit of the COMPASS complex that methylates H3K4</t>
+  </si>
+  <si>
+    <t>GlmU</t>
+  </si>
+  <si>
+    <t>tRNA pseudouridine synthase</t>
+  </si>
+  <si>
+    <t>Acetate/succinate transporter</t>
+  </si>
+  <si>
+    <t>Catalyzes reversible phosphate transfer between ATP and AMP</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L1</t>
+  </si>
+  <si>
+    <t>Involved in cell adhesion</t>
+  </si>
+  <si>
+    <t>Stabilizes TBP binding and recruits RNA polymerase to the pre-initiation complex</t>
+  </si>
+  <si>
+    <t>Cellular processes and signalling</t>
+  </si>
+  <si>
+    <t>eIF2 functions in the early steps of protein synthesis by forming a ternary complex with GTP and initiator tRNA</t>
+  </si>
+  <si>
+    <t>eIF2</t>
+  </si>
+  <si>
+    <t>Function in general translation initiation by promoting the binding of the formylmethionine-tRNA to ribosomes. Seems to function along with eIF2</t>
+  </si>
+  <si>
+    <t>ESP assignments are computational calls supported by DIAMOND and HMMER.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1828,7 +1864,18 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1880,16 +1927,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1950,9 +2002,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2060,8 +2112,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.1640625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="28" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="70" style="1" customWidth="1"/>
     <col min="6" max="6" width="24" style="1" customWidth="1"/>
     <col min="7" max="8" width="28" style="1" customWidth="1"/>
@@ -2070,62 +2123,62 @@
     <col min="11" max="11" width="36" style="1" customWidth="1"/>
     <col min="12" max="12" width="52" style="1" customWidth="1"/>
     <col min="13" max="13" width="55" style="1" customWidth="1"/>
-    <col min="14" max="14" width="80" style="1" customWidth="1"/>
+    <col min="14" max="14" width="171.5" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1">
-      <c r="A1" s="4" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="16" thickTop="1" thickBot="1">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    <row r="1" spans="1:14" s="3" customFormat="1">
+      <c r="A1" s="8" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2133,43 +2186,43 @@
       <c r="C3" s="1">
         <v>0</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>100</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G3" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2177,101 +2230,101 @@
       <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6">
+        <v>100</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7">
-        <v>100</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <v>100</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>100</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -2279,31 +2332,31 @@
       <c r="C7" s="1">
         <v>0</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -2311,31 +2364,31 @@
       <c r="C8" s="1">
         <v>0</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -2343,31 +2396,31 @@
       <c r="C9" s="1">
         <v>1</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B10" s="1">
         <v>5</v>
@@ -2375,31 +2428,31 @@
       <c r="C10" s="1">
         <v>3</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>40</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B11" s="1">
         <v>6</v>
@@ -2407,31 +2460,31 @@
       <c r="C11" s="1">
         <v>4</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>33.333333333333329</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
@@ -2439,31 +2492,31 @@
       <c r="C12" s="1">
         <v>2</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>33.333333333333329</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
@@ -2471,31 +2524,31 @@
       <c r="C13" s="1">
         <v>2</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>33.333333333333329</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B14" s="1">
         <v>4</v>
@@ -2503,43 +2556,43 @@
       <c r="C14" s="1">
         <v>3</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B15" s="1">
         <v>4</v>
@@ -2547,31 +2600,31 @@
       <c r="C15" s="1">
         <v>3</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>76</v>
+        <v>589</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B16" s="1">
         <v>10</v>
@@ -2579,31 +2632,31 @@
       <c r="C16" s="1">
         <v>8</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B17" s="1">
         <v>5</v>
@@ -2611,31 +2664,31 @@
       <c r="C17" s="1">
         <v>4</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B18" s="1">
         <v>5</v>
@@ -2643,31 +2696,31 @@
       <c r="C18" s="1">
         <v>4</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B19" s="1">
         <v>14</v>
@@ -2675,31 +2728,31 @@
       <c r="C19" s="1">
         <v>12</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="6">
         <v>14.285714285714279</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B20" s="1">
         <v>7</v>
@@ -2707,31 +2760,31 @@
       <c r="C20" s="1">
         <v>6</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>14.285714285714279</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B21" s="1">
         <v>22</v>
@@ -2739,31 +2792,31 @@
       <c r="C21" s="1">
         <v>19</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="6">
         <v>13.63636363636363</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B22" s="1">
         <v>8</v>
@@ -2771,31 +2824,31 @@
       <c r="C22" s="1">
         <v>7</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="6">
         <v>12.5</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B23" s="1">
         <v>10</v>
@@ -2803,31 +2856,31 @@
       <c r="C23" s="1">
         <v>9</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="6">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B24" s="1">
         <v>10</v>
@@ -2835,31 +2888,31 @@
       <c r="C24" s="1">
         <v>9</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="6">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B25" s="1">
         <v>31</v>
@@ -2867,31 +2920,31 @@
       <c r="C25" s="1">
         <v>28</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <v>9.67741935483871</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>106</v>
+        <v>604</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B26" s="1">
         <v>15</v>
@@ -2899,31 +2952,31 @@
       <c r="C26" s="1">
         <v>14</v>
       </c>
-      <c r="D26" s="7">
-        <v>6.666666666666667</v>
+      <c r="D26" s="6">
+        <v>6.6666666666666696</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>110</v>
+        <v>590</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B27" s="1">
         <v>17</v>
@@ -2931,43 +2984,43 @@
       <c r="C27" s="1">
         <v>16</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>5.8823529411764701</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="J27" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B28" s="1">
         <v>17</v>
@@ -2975,31 +3028,31 @@
       <c r="C28" s="1">
         <v>16</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="6">
         <v>5.8823529411764701</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B29" s="1">
         <v>99</v>
@@ -3007,43 +3060,43 @@
       <c r="C29" s="1">
         <v>94</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="6">
         <v>5.0505050505050502</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="N29" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B30" s="1">
         <v>23</v>
@@ -3051,31 +3104,31 @@
       <c r="C30" s="1">
         <v>22</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="6">
         <v>4.3478260869565224</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B31" s="1">
         <v>77</v>
@@ -3083,43 +3136,43 @@
       <c r="C31" s="1">
         <v>74</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="6">
         <v>3.8961038961038961</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="N31" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B32" s="1">
         <v>87</v>
@@ -3127,31 +3180,31 @@
       <c r="C32" s="1">
         <v>84</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="6">
         <v>3.4482758620689649</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B33" s="1">
         <v>29</v>
@@ -3159,31 +3212,31 @@
       <c r="C33" s="1">
         <v>28</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="6">
         <v>3.4482758620689649</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B34" s="1">
         <v>30</v>
@@ -3191,31 +3244,31 @@
       <c r="C34" s="1">
         <v>29</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="6">
         <v>3.333333333333333</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B35" s="1">
         <v>301</v>
@@ -3223,43 +3276,43 @@
       <c r="C35" s="1">
         <v>293</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="6">
         <v>2.6578073089701002</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B36" s="1">
         <v>294</v>
@@ -3267,31 +3320,31 @@
       <c r="C36" s="1">
         <v>287</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="6">
         <v>2.3809523809523809</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B37" s="1">
         <v>199</v>
@@ -3299,31 +3352,31 @@
       <c r="C37" s="1">
         <v>195</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="6">
         <v>2.0100502512562808</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>146</v>
+        <v>572</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B38" s="1">
         <v>52</v>
@@ -3331,31 +3384,31 @@
       <c r="C38" s="1">
         <v>51</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="6">
         <v>1.9230769230769229</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>149</v>
+        <v>593</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="1" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B39" s="1">
         <v>313</v>
@@ -3363,31 +3416,31 @@
       <c r="C39" s="1">
         <v>307</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="6">
         <v>1.9169329073482431</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>152</v>
+        <v>592</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B40" s="1">
         <v>62</v>
@@ -3395,31 +3448,31 @@
       <c r="C40" s="1">
         <v>61</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="6">
         <v>1.612903225806452</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>155</v>
+        <v>594</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B41" s="1">
         <v>62</v>
@@ -3427,43 +3480,43 @@
       <c r="C41" s="1">
         <v>61</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="6">
         <v>1.612903225806452</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B42" s="1">
         <v>170</v>
@@ -3471,43 +3524,43 @@
       <c r="C42" s="1">
         <v>168</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="6">
         <v>1.1764705882352939</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="1" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B43" s="1">
         <v>94</v>
@@ -3515,31 +3568,31 @@
       <c r="C43" s="1">
         <v>93</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="6">
         <v>1.063829787234043</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="1" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B44" s="1">
         <v>100</v>
@@ -3547,31 +3600,31 @@
       <c r="C44" s="1">
         <v>99</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="6">
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="1" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B45" s="1">
         <v>239</v>
@@ -3579,31 +3632,31 @@
       <c r="C45" s="1">
         <v>237</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="6">
         <v>0.83682008368200833</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="1" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B46" s="1">
         <v>142</v>
@@ -3611,43 +3664,43 @@
       <c r="C46" s="1">
         <v>141</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="6">
         <v>0.70422535211267612</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="N46" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B47" s="1">
         <v>172</v>
@@ -3655,31 +3708,31 @@
       <c r="C47" s="1">
         <v>172</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="6">
         <v>0</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="1" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B48" s="1">
         <v>107</v>
@@ -3687,31 +3740,31 @@
       <c r="C48" s="1">
         <v>107</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="6">
         <v>0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B49" s="1">
         <v>97</v>
@@ -3719,31 +3772,31 @@
       <c r="C49" s="1">
         <v>97</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="6">
         <v>0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B50" s="1">
         <v>94</v>
@@ -3751,31 +3804,31 @@
       <c r="C50" s="1">
         <v>94</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="6">
         <v>0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B51" s="1">
         <v>65</v>
@@ -3783,31 +3836,31 @@
       <c r="C51" s="1">
         <v>65</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D51" s="6">
         <v>0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>193</v>
+        <v>573</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="1" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B52" s="1">
         <v>34</v>
@@ -3815,31 +3868,31 @@
       <c r="C52" s="1">
         <v>34</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="6">
         <v>0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>196</v>
+        <v>574</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B53" s="1">
         <v>29</v>
@@ -3847,31 +3900,31 @@
       <c r="C53" s="1">
         <v>29</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="6">
         <v>0</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="1" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="B54" s="1">
         <v>28</v>
@@ -3879,31 +3932,31 @@
       <c r="C54" s="1">
         <v>28</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="6">
         <v>0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="1" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B55" s="1">
         <v>27</v>
@@ -3911,31 +3964,31 @@
       <c r="C55" s="1">
         <v>27</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="6">
         <v>0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="1" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="B56" s="1">
         <v>23</v>
@@ -3943,31 +3996,31 @@
       <c r="C56" s="1">
         <v>23</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="6">
         <v>0</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="1" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B57" s="1">
         <v>21</v>
@@ -3975,31 +4028,31 @@
       <c r="C57" s="1">
         <v>21</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="6">
         <v>0</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="1" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B58" s="1">
         <v>18</v>
@@ -4007,31 +4060,31 @@
       <c r="C58" s="1">
         <v>18</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="6">
         <v>0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>211</v>
+        <v>575</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="1" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B59" s="1">
         <v>18</v>
@@ -4039,31 +4092,31 @@
       <c r="C59" s="1">
         <v>18</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="6">
         <v>0</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="1" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B60" s="1">
         <v>18</v>
@@ -4071,31 +4124,31 @@
       <c r="C60" s="1">
         <v>18</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="6">
         <v>0</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="1" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B61" s="1">
         <v>17</v>
@@ -4103,31 +4156,31 @@
       <c r="C61" s="1">
         <v>17</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="6">
         <v>0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>219</v>
+        <v>595</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="1" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B62" s="1">
         <v>15</v>
@@ -4135,31 +4188,31 @@
       <c r="C62" s="1">
         <v>15</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="6">
         <v>0</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>222</v>
+        <v>576</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="1" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="B63" s="1">
         <v>15</v>
@@ -4167,31 +4220,31 @@
       <c r="C63" s="1">
         <v>15</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D63" s="6">
         <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="1" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="B64" s="1">
         <v>14</v>
@@ -4199,31 +4252,31 @@
       <c r="C64" s="1">
         <v>14</v>
       </c>
-      <c r="D64" s="7">
+      <c r="D64" s="6">
         <v>0</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="1" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="B65" s="1">
         <v>14</v>
@@ -4231,31 +4284,31 @@
       <c r="C65" s="1">
         <v>14</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="6">
         <v>0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="1" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B66" s="1">
         <v>13</v>
@@ -4263,31 +4316,31 @@
       <c r="C66" s="1">
         <v>13</v>
       </c>
-      <c r="D66" s="7">
+      <c r="D66" s="6">
         <v>0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="1" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="B67" s="1">
         <v>13</v>
@@ -4295,31 +4348,31 @@
       <c r="C67" s="1">
         <v>13</v>
       </c>
-      <c r="D67" s="7">
+      <c r="D67" s="6">
         <v>0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="1" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="B68" s="1">
         <v>13</v>
@@ -4327,31 +4380,31 @@
       <c r="C68" s="1">
         <v>13</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="6">
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="1" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="B69" s="1">
         <v>12</v>
@@ -4359,31 +4412,31 @@
       <c r="C69" s="1">
         <v>12</v>
       </c>
-      <c r="D69" s="7">
+      <c r="D69" s="6">
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>241</v>
+        <v>596</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="1" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="B70" s="1">
         <v>11</v>
@@ -4391,31 +4444,31 @@
       <c r="C70" s="1">
         <v>11</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="6">
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="1" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B71" s="1">
         <v>10</v>
@@ -4423,31 +4476,31 @@
       <c r="C71" s="1">
         <v>10</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="6">
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="1" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="B72" s="1">
         <v>9</v>
@@ -4455,31 +4508,31 @@
       <c r="C72" s="1">
         <v>9</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D72" s="6">
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>250</v>
+        <v>577</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="1" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B73" s="1">
         <v>8</v>
@@ -4487,31 +4540,31 @@
       <c r="C73" s="1">
         <v>8</v>
       </c>
-      <c r="D73" s="7">
+      <c r="D73" s="6">
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>253</v>
+        <v>578</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="1" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B74" s="1">
         <v>8</v>
@@ -4519,43 +4572,43 @@
       <c r="C74" s="1">
         <v>8</v>
       </c>
-      <c r="D74" s="7">
+      <c r="D74" s="6">
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H74" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="J74" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="1" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="B75" s="1">
         <v>7</v>
@@ -4563,31 +4616,31 @@
       <c r="C75" s="1">
         <v>7</v>
       </c>
-      <c r="D75" s="7">
+      <c r="D75" s="6">
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="1" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="B76" s="1">
         <v>6</v>
@@ -4595,31 +4648,31 @@
       <c r="C76" s="1">
         <v>6</v>
       </c>
-      <c r="D76" s="7">
+      <c r="D76" s="6">
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="1" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="B77" s="1">
         <v>6</v>
@@ -4627,31 +4680,31 @@
       <c r="C77" s="1">
         <v>6</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D77" s="6">
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="1" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="B78" s="1">
         <v>6</v>
@@ -4659,31 +4712,31 @@
       <c r="C78" s="1">
         <v>6</v>
       </c>
-      <c r="D78" s="7">
+      <c r="D78" s="6">
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>267</v>
+        <v>597</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="1" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="B79" s="1">
         <v>6</v>
@@ -4691,31 +4744,31 @@
       <c r="C79" s="1">
         <v>6</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D79" s="6">
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="1" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="B80" s="1">
         <v>6</v>
@@ -4723,31 +4776,31 @@
       <c r="C80" s="1">
         <v>6</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D80" s="6">
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="1" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="B81" s="1">
         <v>6</v>
@@ -4755,31 +4808,31 @@
       <c r="C81" s="1">
         <v>6</v>
       </c>
-      <c r="D81" s="7">
+      <c r="D81" s="6">
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>273</v>
+        <v>598</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="1" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="B82" s="1">
         <v>6</v>
@@ -4787,31 +4840,31 @@
       <c r="C82" s="1">
         <v>6</v>
       </c>
-      <c r="D82" s="7">
+      <c r="D82" s="6">
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="1" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="B83" s="1">
         <v>5</v>
@@ -4819,31 +4872,31 @@
       <c r="C83" s="1">
         <v>5</v>
       </c>
-      <c r="D83" s="7">
+      <c r="D83" s="6">
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="1" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="B84" s="1">
         <v>5</v>
@@ -4851,31 +4904,31 @@
       <c r="C84" s="1">
         <v>5</v>
       </c>
-      <c r="D84" s="7">
+      <c r="D84" s="6">
         <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="1" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="B85" s="1">
         <v>5</v>
@@ -4883,31 +4936,31 @@
       <c r="C85" s="1">
         <v>5</v>
       </c>
-      <c r="D85" s="7">
+      <c r="D85" s="6">
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="1" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="B86" s="1">
         <v>4</v>
@@ -4915,31 +4968,31 @@
       <c r="C86" s="1">
         <v>4</v>
       </c>
-      <c r="D86" s="7">
+      <c r="D86" s="6">
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="1" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="B87" s="1">
         <v>4</v>
@@ -4947,31 +5000,31 @@
       <c r="C87" s="1">
         <v>4</v>
       </c>
-      <c r="D87" s="7">
+      <c r="D87" s="6">
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="1" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="B88" s="1">
         <v>4</v>
@@ -4979,31 +5032,31 @@
       <c r="C88" s="1">
         <v>4</v>
       </c>
-      <c r="D88" s="7">
+      <c r="D88" s="6">
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I88" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G88" s="1" t="s">
+      <c r="N88" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N88" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="1" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="B89" s="1">
         <v>4</v>
@@ -5011,31 +5064,31 @@
       <c r="C89" s="1">
         <v>4</v>
       </c>
-      <c r="D89" s="7">
+      <c r="D89" s="6">
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="1" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="B90" s="1">
         <v>4</v>
@@ -5043,43 +5096,43 @@
       <c r="C90" s="1">
         <v>4</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="6">
         <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="G90" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H90" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="I90" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I90" s="1" t="s">
+      <c r="J90" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J90" s="1" t="s">
+      <c r="K90" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K90" s="1" t="s">
+      <c r="L90" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L90" s="1" t="s">
+      <c r="M90" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M90" s="1" t="s">
+      <c r="N90" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="N90" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="1" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="B91" s="1">
         <v>4</v>
@@ -5087,31 +5140,31 @@
       <c r="C91" s="1">
         <v>4</v>
       </c>
-      <c r="D91" s="7">
+      <c r="D91" s="6">
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="1" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="B92" s="1">
         <v>4</v>
@@ -5119,31 +5172,31 @@
       <c r="C92" s="1">
         <v>4</v>
       </c>
-      <c r="D92" s="7">
+      <c r="D92" s="6">
         <v>0</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="1" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B93" s="1">
         <v>4</v>
@@ -5151,31 +5204,31 @@
       <c r="C93" s="1">
         <v>4</v>
       </c>
-      <c r="D93" s="7">
+      <c r="D93" s="6">
         <v>0</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>302</v>
+        <v>579</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="1" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="B94" s="1">
         <v>3</v>
@@ -5183,31 +5236,31 @@
       <c r="C94" s="1">
         <v>3</v>
       </c>
-      <c r="D94" s="7">
+      <c r="D94" s="6">
         <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="1" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="B95" s="1">
         <v>3</v>
@@ -5215,31 +5268,31 @@
       <c r="C95" s="1">
         <v>3</v>
       </c>
-      <c r="D95" s="7">
+      <c r="D95" s="6">
         <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="1" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="B96" s="1">
         <v>3</v>
@@ -5247,31 +5300,31 @@
       <c r="C96" s="1">
         <v>3</v>
       </c>
-      <c r="D96" s="7">
+      <c r="D96" s="6">
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="1" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="B97" s="1">
         <v>3</v>
@@ -5279,37 +5332,37 @@
       <c r="C97" s="1">
         <v>3</v>
       </c>
-      <c r="D97" s="7">
+      <c r="D97" s="6">
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="1" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="B98" s="1">
         <v>3</v>
@@ -5317,31 +5370,31 @@
       <c r="C98" s="1">
         <v>3</v>
       </c>
-      <c r="D98" s="7">
+      <c r="D98" s="6">
         <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="1" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="B99" s="1">
         <v>3</v>
@@ -5349,43 +5402,43 @@
       <c r="C99" s="1">
         <v>3</v>
       </c>
-      <c r="D99" s="7">
+      <c r="D99" s="6">
         <v>0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>321</v>
+        <v>580</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="1" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="B100" s="1">
         <v>3</v>
@@ -5393,31 +5446,31 @@
       <c r="C100" s="1">
         <v>3</v>
       </c>
-      <c r="D100" s="7">
+      <c r="D100" s="6">
         <v>0</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="1" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="B101" s="1">
         <v>3</v>
@@ -5425,43 +5478,43 @@
       <c r="C101" s="1">
         <v>3</v>
       </c>
-      <c r="D101" s="7">
+      <c r="D101" s="6">
         <v>0</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="1" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="B102" s="1">
         <v>3</v>
@@ -5469,31 +5522,31 @@
       <c r="C102" s="1">
         <v>3</v>
       </c>
-      <c r="D102" s="7">
+      <c r="D102" s="6">
         <v>0</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="1" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="B103" s="1">
         <v>3</v>
@@ -5501,31 +5554,31 @@
       <c r="C103" s="1">
         <v>3</v>
       </c>
-      <c r="D103" s="7">
+      <c r="D103" s="6">
         <v>0</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="1" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="B104" s="1">
         <v>3</v>
@@ -5533,31 +5586,31 @@
       <c r="C104" s="1">
         <v>3</v>
       </c>
-      <c r="D104" s="7">
+      <c r="D104" s="6">
         <v>0</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="1" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="B105" s="1">
         <v>3</v>
@@ -5565,43 +5618,43 @@
       <c r="C105" s="1">
         <v>3</v>
       </c>
-      <c r="D105" s="7">
+      <c r="D105" s="6">
         <v>0</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="1" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="B106" s="1">
         <v>3</v>
@@ -5609,31 +5662,31 @@
       <c r="C106" s="1">
         <v>3</v>
       </c>
-      <c r="D106" s="7">
+      <c r="D106" s="6">
         <v>0</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="1" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="B107" s="1">
         <v>3</v>
@@ -5641,31 +5694,31 @@
       <c r="C107" s="1">
         <v>3</v>
       </c>
-      <c r="D107" s="7">
+      <c r="D107" s="6">
         <v>0</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="1" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="B108" s="1">
         <v>3</v>
@@ -5673,31 +5726,31 @@
       <c r="C108" s="1">
         <v>3</v>
       </c>
-      <c r="D108" s="7">
+      <c r="D108" s="6">
         <v>0</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>348</v>
+        <v>581</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="1" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="B109" s="1">
         <v>3</v>
@@ -5705,31 +5758,31 @@
       <c r="C109" s="1">
         <v>3</v>
       </c>
-      <c r="D109" s="7">
+      <c r="D109" s="6">
         <v>0</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="1" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="B110" s="1">
         <v>3</v>
@@ -5737,31 +5790,31 @@
       <c r="C110" s="1">
         <v>3</v>
       </c>
-      <c r="D110" s="7">
+      <c r="D110" s="6">
         <v>0</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="1" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="B111" s="1">
         <v>2</v>
@@ -5769,31 +5822,31 @@
       <c r="C111" s="1">
         <v>2</v>
       </c>
-      <c r="D111" s="7">
+      <c r="D111" s="6">
         <v>0</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="1" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="B112" s="1">
         <v>2</v>
@@ -5801,31 +5854,31 @@
       <c r="C112" s="1">
         <v>2</v>
       </c>
-      <c r="D112" s="7">
+      <c r="D112" s="6">
         <v>0</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="1" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B113" s="1">
         <v>2</v>
@@ -5833,31 +5886,31 @@
       <c r="C113" s="1">
         <v>2</v>
       </c>
-      <c r="D113" s="7">
+      <c r="D113" s="6">
         <v>0</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>361</v>
+        <v>583</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="1" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="B114" s="1">
         <v>2</v>
@@ -5865,31 +5918,31 @@
       <c r="C114" s="1">
         <v>2</v>
       </c>
-      <c r="D114" s="7">
+      <c r="D114" s="6">
         <v>0</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="1" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="B115" s="1">
         <v>2</v>
@@ -5897,31 +5950,31 @@
       <c r="C115" s="1">
         <v>2</v>
       </c>
-      <c r="D115" s="7">
+      <c r="D115" s="6">
         <v>0</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="1" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="B116" s="1">
         <v>2</v>
@@ -5929,31 +5982,31 @@
       <c r="C116" s="1">
         <v>2</v>
       </c>
-      <c r="D116" s="7">
+      <c r="D116" s="6">
         <v>0</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="1" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="B117" s="1">
         <v>2</v>
@@ -5961,31 +6014,31 @@
       <c r="C117" s="1">
         <v>2</v>
       </c>
-      <c r="D117" s="7">
+      <c r="D117" s="6">
         <v>0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="1" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="B118" s="1">
         <v>2</v>
@@ -5993,31 +6046,31 @@
       <c r="C118" s="1">
         <v>2</v>
       </c>
-      <c r="D118" s="7">
+      <c r="D118" s="6">
         <v>0</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="1" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="B119" s="1">
         <v>2</v>
@@ -6025,31 +6078,31 @@
       <c r="C119" s="1">
         <v>2</v>
       </c>
-      <c r="D119" s="7">
+      <c r="D119" s="6">
         <v>0</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="1" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="B120" s="1">
         <v>2</v>
@@ -6057,31 +6110,31 @@
       <c r="C120" s="1">
         <v>2</v>
       </c>
-      <c r="D120" s="7">
+      <c r="D120" s="6">
         <v>0</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="1" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="B121" s="1">
         <v>2</v>
@@ -6089,31 +6142,31 @@
       <c r="C121" s="1">
         <v>2</v>
       </c>
-      <c r="D121" s="7">
+      <c r="D121" s="6">
         <v>0</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="1" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="B122" s="1">
         <v>2</v>
@@ -6121,31 +6174,31 @@
       <c r="C122" s="1">
         <v>2</v>
       </c>
-      <c r="D122" s="7">
+      <c r="D122" s="6">
         <v>0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="1" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="B123" s="1">
         <v>2</v>
@@ -6153,31 +6206,31 @@
       <c r="C123" s="1">
         <v>2</v>
       </c>
-      <c r="D123" s="7">
+      <c r="D123" s="6">
         <v>0</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="1" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="B124" s="1">
         <v>2</v>
@@ -6185,31 +6238,31 @@
       <c r="C124" s="1">
         <v>2</v>
       </c>
-      <c r="D124" s="7">
+      <c r="D124" s="6">
         <v>0</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="N124" s="1" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="1" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="B125" s="1">
         <v>1</v>
@@ -6217,31 +6270,31 @@
       <c r="C125" s="1">
         <v>1</v>
       </c>
-      <c r="D125" s="7">
+      <c r="D125" s="6">
         <v>0</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="1" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="B126" s="1">
         <v>1</v>
@@ -6249,31 +6302,31 @@
       <c r="C126" s="1">
         <v>1</v>
       </c>
-      <c r="D126" s="7">
+      <c r="D126" s="6">
         <v>0</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N126" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="1" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="B127" s="1">
         <v>1</v>
@@ -6281,31 +6334,31 @@
       <c r="C127" s="1">
         <v>1</v>
       </c>
-      <c r="D127" s="7">
+      <c r="D127" s="6">
         <v>0</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="N127" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="1" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="B128" s="1">
         <v>1</v>
@@ -6313,31 +6366,31 @@
       <c r="C128" s="1">
         <v>1</v>
       </c>
-      <c r="D128" s="7">
+      <c r="D128" s="6">
         <v>0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="1" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="B129" s="1">
         <v>1</v>
@@ -6345,31 +6398,31 @@
       <c r="C129" s="1">
         <v>1</v>
       </c>
-      <c r="D129" s="7">
+      <c r="D129" s="6">
         <v>0</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>405</v>
+        <v>599</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N129" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="1" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="B130" s="1">
         <v>1</v>
@@ -6377,43 +6430,43 @@
       <c r="C130" s="1">
         <v>1</v>
       </c>
-      <c r="D130" s="7">
+      <c r="D130" s="6">
         <v>0</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>413</v>
+        <v>584</v>
       </c>
       <c r="G130" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H130" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H130" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="I130" s="1" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="N130" s="1" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="1" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
       <c r="B131" s="1">
         <v>1</v>
@@ -6421,31 +6474,31 @@
       <c r="C131" s="1">
         <v>1</v>
       </c>
-      <c r="D131" s="7">
+      <c r="D131" s="6">
         <v>0</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N131" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="1" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="B132" s="1">
         <v>1</v>
@@ -6453,31 +6506,31 @@
       <c r="C132" s="1">
         <v>1</v>
       </c>
-      <c r="D132" s="7">
+      <c r="D132" s="6">
         <v>0</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N132" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="1" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="B133" s="1">
         <v>1</v>
@@ -6485,31 +6538,31 @@
       <c r="C133" s="1">
         <v>1</v>
       </c>
-      <c r="D133" s="7">
+      <c r="D133" s="6">
         <v>0</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="1" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="B134" s="1">
         <v>1</v>
@@ -6517,31 +6570,31 @@
       <c r="C134" s="1">
         <v>1</v>
       </c>
-      <c r="D134" s="7">
+      <c r="D134" s="6">
         <v>0</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>592</v>
+        <v>396</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="1" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="B135" s="1">
         <v>1</v>
@@ -6549,31 +6602,31 @@
       <c r="C135" s="1">
         <v>1</v>
       </c>
-      <c r="D135" s="7">
+      <c r="D135" s="6">
         <v>0</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="1" t="s">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="B136" s="1">
         <v>1</v>
@@ -6581,31 +6634,31 @@
       <c r="C136" s="1">
         <v>1</v>
       </c>
-      <c r="D136" s="7">
+      <c r="D136" s="6">
         <v>0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="1" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="B137" s="1">
         <v>1</v>
@@ -6613,31 +6666,31 @@
       <c r="C137" s="1">
         <v>1</v>
       </c>
-      <c r="D137" s="7">
+      <c r="D137" s="6">
         <v>0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="1" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="B138" s="1">
         <v>1</v>
@@ -6645,31 +6698,31 @@
       <c r="C138" s="1">
         <v>1</v>
       </c>
-      <c r="D138" s="7">
+      <c r="D138" s="6">
         <v>0</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>432</v>
+        <v>585</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="1" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="B139" s="1">
         <v>1</v>
@@ -6677,31 +6730,31 @@
       <c r="C139" s="1">
         <v>1</v>
       </c>
-      <c r="D139" s="7">
+      <c r="D139" s="6">
         <v>0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="1" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="B140" s="1">
         <v>1</v>
@@ -6709,31 +6762,31 @@
       <c r="C140" s="1">
         <v>1</v>
       </c>
-      <c r="D140" s="7">
+      <c r="D140" s="6">
         <v>0</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="1" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="B141" s="1">
         <v>1</v>
@@ -6741,31 +6794,31 @@
       <c r="C141" s="1">
         <v>1</v>
       </c>
-      <c r="D141" s="7">
+      <c r="D141" s="6">
         <v>0</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="1" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="B142" s="1">
         <v>1</v>
@@ -6773,31 +6826,31 @@
       <c r="C142" s="1">
         <v>1</v>
       </c>
-      <c r="D142" s="7">
+      <c r="D142" s="6">
         <v>0</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="1" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="B143" s="1">
         <v>1</v>
@@ -6805,31 +6858,31 @@
       <c r="C143" s="1">
         <v>1</v>
       </c>
-      <c r="D143" s="7">
+      <c r="D143" s="6">
         <v>0</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="1" t="s">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="B144" s="1">
         <v>1</v>
@@ -6837,31 +6890,31 @@
       <c r="C144" s="1">
         <v>1</v>
       </c>
-      <c r="D144" s="7">
+      <c r="D144" s="6">
         <v>0</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="1" t="s">
-        <v>447</v>
+        <v>421</v>
       </c>
       <c r="B145" s="1">
         <v>1</v>
@@ -6869,43 +6922,43 @@
       <c r="C145" s="1">
         <v>1</v>
       </c>
-      <c r="D145" s="7">
+      <c r="D145" s="6">
         <v>0</v>
       </c>
       <c r="E145" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L145" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M145" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="N145" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H145" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J145" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K145" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L145" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M145" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="N145" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="1" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="B146" s="1">
         <v>1</v>
@@ -6913,31 +6966,31 @@
       <c r="C146" s="1">
         <v>1</v>
       </c>
-      <c r="D146" s="7">
+      <c r="D146" s="6">
         <v>0</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="1" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="B147" s="1">
         <v>1</v>
@@ -6945,31 +6998,31 @@
       <c r="C147" s="1">
         <v>1</v>
       </c>
-      <c r="D147" s="7">
+      <c r="D147" s="6">
         <v>0</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="1" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="B148" s="1">
         <v>1</v>
@@ -6977,31 +7030,31 @@
       <c r="C148" s="1">
         <v>1</v>
       </c>
-      <c r="D148" s="7">
+      <c r="D148" s="6">
         <v>0</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="1" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="B149" s="1">
         <v>1</v>
@@ -7009,31 +7062,31 @@
       <c r="C149" s="1">
         <v>1</v>
       </c>
-      <c r="D149" s="7">
+      <c r="D149" s="6">
         <v>0</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="1" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="B150" s="1">
         <v>1</v>
@@ -7041,31 +7094,31 @@
       <c r="C150" s="1">
         <v>1</v>
       </c>
-      <c r="D150" s="7">
+      <c r="D150" s="6">
         <v>0</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="1" t="s">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="B151" s="1">
         <v>1</v>
@@ -7073,31 +7126,31 @@
       <c r="C151" s="1">
         <v>1</v>
       </c>
-      <c r="D151" s="7">
+      <c r="D151" s="6">
         <v>0</v>
       </c>
       <c r="E151" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I151" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F151" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G151" s="1" t="s">
+      <c r="N151" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="H151" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N151" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="1" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="B152" s="1">
         <v>1</v>
@@ -7105,31 +7158,31 @@
       <c r="C152" s="1">
         <v>1</v>
       </c>
-      <c r="D152" s="7">
+      <c r="D152" s="6">
         <v>0</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="1" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="B153" s="1">
         <v>1</v>
@@ -7137,31 +7190,31 @@
       <c r="C153" s="1">
         <v>1</v>
       </c>
-      <c r="D153" s="7">
+      <c r="D153" s="6">
         <v>0</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>110</v>
+        <v>591</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="1" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="B154" s="1">
         <v>1</v>
@@ -7169,31 +7222,31 @@
       <c r="C154" s="1">
         <v>1</v>
       </c>
-      <c r="D154" s="7">
+      <c r="D154" s="6">
         <v>0</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="1" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="B155" s="1">
         <v>1</v>
@@ -7201,43 +7254,43 @@
       <c r="C155" s="1">
         <v>1</v>
       </c>
-      <c r="D155" s="7">
+      <c r="D155" s="6">
         <v>0</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>472</v>
+        <v>446</v>
       </c>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="1" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="B156" s="1">
         <v>1</v>
@@ -7245,31 +7298,31 @@
       <c r="C156" s="1">
         <v>1</v>
       </c>
-      <c r="D156" s="7">
+      <c r="D156" s="6">
         <v>0</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>475</v>
+        <v>586</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="1" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="B157" s="1">
         <v>1</v>
@@ -7277,31 +7330,31 @@
       <c r="C157" s="1">
         <v>1</v>
       </c>
-      <c r="D157" s="7">
+      <c r="D157" s="6">
         <v>0</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="1" t="s">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="B158" s="1">
         <v>1</v>
@@ -7309,31 +7362,31 @@
       <c r="C158" s="1">
         <v>1</v>
       </c>
-      <c r="D158" s="7">
+      <c r="D158" s="6">
         <v>0</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>481</v>
+        <v>454</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="1" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="B159" s="1">
         <v>1</v>
@@ -7341,31 +7394,31 @@
       <c r="C159" s="1">
         <v>1</v>
       </c>
-      <c r="D159" s="7">
+      <c r="D159" s="6">
         <v>0</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="1" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="B160" s="1">
         <v>1</v>
@@ -7373,31 +7426,31 @@
       <c r="C160" s="1">
         <v>1</v>
       </c>
-      <c r="D160" s="7">
+      <c r="D160" s="6">
         <v>0</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="1" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="B161" s="1">
         <v>1</v>
@@ -7405,31 +7458,31 @@
       <c r="C161" s="1">
         <v>1</v>
       </c>
-      <c r="D161" s="7">
+      <c r="D161" s="6">
         <v>0</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="1" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="B162" s="1">
         <v>1</v>
@@ -7437,43 +7490,43 @@
       <c r="C162" s="1">
         <v>1</v>
       </c>
-      <c r="D162" s="7">
+      <c r="D162" s="6">
         <v>0</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="M162" s="1" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="N162" s="1" t="s">
-        <v>472</v>
+        <v>446</v>
       </c>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="1" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="B163" s="1">
         <v>1</v>
@@ -7481,37 +7534,37 @@
       <c r="C163" s="1">
         <v>1</v>
       </c>
-      <c r="D163" s="7">
+      <c r="D163" s="6">
         <v>0</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>498</v>
+        <v>467</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="M163" s="1" t="s">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>497</v>
+        <v>471</v>
       </c>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="1" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="B164" s="1">
         <v>1</v>
@@ -7519,31 +7572,31 @@
       <c r="C164" s="1">
         <v>1</v>
       </c>
-      <c r="D164" s="7">
+      <c r="D164" s="6">
         <v>0</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="1" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="B165" s="1">
         <v>1</v>
@@ -7551,31 +7604,31 @@
       <c r="C165" s="1">
         <v>1</v>
       </c>
-      <c r="D165" s="7">
+      <c r="D165" s="6">
         <v>0</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>503</v>
+        <v>476</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>348</v>
+        <v>582</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="1" t="s">
-        <v>504</v>
+        <v>477</v>
       </c>
       <c r="B166" s="1">
         <v>1</v>
@@ -7583,37 +7636,37 @@
       <c r="C166" s="1">
         <v>1</v>
       </c>
-      <c r="D166" s="7">
+      <c r="D166" s="6">
         <v>0</v>
       </c>
       <c r="E166" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L166" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M166" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F166" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G166" s="1" t="s">
+      <c r="N166" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="H166" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L166" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M166" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N166" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="1" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="B167" s="1">
         <v>1</v>
@@ -7621,31 +7674,31 @@
       <c r="C167" s="1">
         <v>1</v>
       </c>
-      <c r="D167" s="7">
+      <c r="D167" s="6">
         <v>0</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="1" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="B168" s="1">
         <v>1</v>
@@ -7653,31 +7706,31 @@
       <c r="C168" s="1">
         <v>1</v>
       </c>
-      <c r="D168" s="7">
+      <c r="D168" s="6">
         <v>0</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>509</v>
+        <v>482</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>509</v>
+        <v>482</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="1" t="s">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="B169" s="1">
         <v>1</v>
@@ -7685,31 +7738,31 @@
       <c r="C169" s="1">
         <v>1</v>
       </c>
-      <c r="D169" s="7">
+      <c r="D169" s="6">
         <v>0</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>512</v>
+        <v>485</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="1" t="s">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="B170" s="1">
         <v>1</v>
@@ -7717,31 +7770,31 @@
       <c r="C170" s="1">
         <v>1</v>
       </c>
-      <c r="D170" s="7">
+      <c r="D170" s="6">
         <v>0</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>514</v>
+        <v>487</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>514</v>
+        <v>487</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N170" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="1" t="s">
-        <v>515</v>
+        <v>488</v>
       </c>
       <c r="B171" s="1">
         <v>1</v>
@@ -7749,31 +7802,31 @@
       <c r="C171" s="1">
         <v>1</v>
       </c>
-      <c r="D171" s="7">
+      <c r="D171" s="6">
         <v>0</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>516</v>
+        <v>489</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>517</v>
+        <v>490</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N171" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="1" t="s">
-        <v>518</v>
+        <v>491</v>
       </c>
       <c r="B172" s="1">
         <v>1</v>
@@ -7781,31 +7834,31 @@
       <c r="C172" s="1">
         <v>1</v>
       </c>
-      <c r="D172" s="7">
+      <c r="D172" s="6">
         <v>0</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>519</v>
+        <v>492</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>520</v>
+        <v>587</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N172" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="1" t="s">
-        <v>521</v>
+        <v>493</v>
       </c>
       <c r="B173" s="1">
         <v>1</v>
@@ -7813,31 +7866,31 @@
       <c r="C173" s="1">
         <v>1</v>
       </c>
-      <c r="D173" s="7">
+      <c r="D173" s="6">
         <v>0</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>522</v>
+        <v>494</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>523</v>
+        <v>495</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N173" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="1" t="s">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="B174" s="1">
         <v>1</v>
@@ -7845,43 +7898,43 @@
       <c r="C174" s="1">
         <v>1</v>
       </c>
-      <c r="D174" s="7">
+      <c r="D174" s="6">
         <v>0</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="G174" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H174" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H174" s="1" t="s">
+      <c r="I174" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I174" s="1" t="s">
+      <c r="J174" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J174" s="1" t="s">
+      <c r="K174" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K174" s="1" t="s">
+      <c r="L174" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L174" s="1" t="s">
+      <c r="M174" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M174" s="1" t="s">
+      <c r="N174" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="N174" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="1" t="s">
-        <v>525</v>
+        <v>497</v>
       </c>
       <c r="B175" s="1">
         <v>1</v>
@@ -7889,37 +7942,37 @@
       <c r="C175" s="1">
         <v>1</v>
       </c>
-      <c r="D175" s="7">
+      <c r="D175" s="6">
         <v>0</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>530</v>
+        <v>588</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H175" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I175" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I175" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="L175" s="1" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="M175" s="1" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="N175" s="1" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="1" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="B176" s="1">
         <v>1</v>
@@ -7927,31 +7980,31 @@
       <c r="C176" s="1">
         <v>1</v>
       </c>
-      <c r="D176" s="7">
+      <c r="D176" s="6">
         <v>0</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>533</v>
+        <v>504</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N176" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="1" t="s">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="B177" s="1">
         <v>1</v>
@@ -7959,31 +8012,31 @@
       <c r="C177" s="1">
         <v>1</v>
       </c>
-      <c r="D177" s="7">
+      <c r="D177" s="6">
         <v>0</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N177" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="1" t="s">
-        <v>537</v>
+        <v>508</v>
       </c>
       <c r="B178" s="1">
         <v>1</v>
@@ -7991,43 +8044,43 @@
       <c r="C178" s="1">
         <v>1</v>
       </c>
-      <c r="D178" s="7">
+      <c r="D178" s="6">
         <v>0</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>538</v>
+        <v>509</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>539</v>
+        <v>600</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="K178" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="M178" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="1" t="s">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="B179" s="1">
         <v>1</v>
@@ -8035,31 +8088,31 @@
       <c r="C179" s="1">
         <v>1</v>
       </c>
-      <c r="D179" s="7">
+      <c r="D179" s="6">
         <v>0</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>541</v>
+        <v>511</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>541</v>
+        <v>511</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N179" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="1" t="s">
-        <v>542</v>
+        <v>512</v>
       </c>
       <c r="B180" s="1">
         <v>1</v>
@@ -8067,65 +8120,69 @@
       <c r="C180" s="1">
         <v>1</v>
       </c>
-      <c r="D180" s="7">
+      <c r="D180" s="6">
         <v>0</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>543</v>
+        <v>513</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>544</v>
+        <v>514</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>16</v>
+        <v>601</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14" ht="15" thickBot="1">
-      <c r="A181" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="B181" s="6">
-        <v>1</v>
-      </c>
-      <c r="C181" s="6">
-        <v>1</v>
-      </c>
-      <c r="D181" s="8">
-        <v>0</v>
-      </c>
-      <c r="E181" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="F181" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="G181" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H181" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I181" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J181" s="6"/>
-      <c r="K181" s="6"/>
-      <c r="L181" s="6"/>
-      <c r="M181" s="6"/>
-      <c r="N181" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14" ht="15" thickTop="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14">
+      <c r="A181" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="B181" s="5">
+        <v>1</v>
+      </c>
+      <c r="C181" s="5">
+        <v>1</v>
+      </c>
+      <c r="D181" s="7">
+        <v>0</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H181" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I181" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J181" s="5"/>
+      <c r="K181" s="5"/>
+      <c r="L181" s="5"/>
+      <c r="M181" s="5"/>
+      <c r="N181" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14">
+      <c r="A182" s="11" t="s">
+        <v>605</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8133,11 +8190,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="28" style="1" customWidth="1"/>
-    <col min="2" max="2" width="40" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24" style="1" customWidth="1"/>
+    <col min="2" max="2" width="69.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="1" customWidth="1"/>
     <col min="5" max="5" width="24" style="1" customWidth="1"/>
@@ -8150,389 +8207,445 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
-        <v>548</v>
+        <v>518</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>549</v>
+        <v>519</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>552</v>
+        <v>522</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>553</v>
+        <v>523</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>554</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>555</v>
+        <v>525</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>561</v>
+        <v>531</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>562</v>
+        <v>532</v>
       </c>
       <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>563</v>
+        <v>533</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>565</v>
+        <v>535</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>566</v>
+        <v>536</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>567</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>568</v>
+        <v>538</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>569</v>
+        <v>539</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>572</v>
+        <v>542</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>575</v>
+        <v>545</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>577</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>578</v>
+        <v>548</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>579</v>
+        <v>549</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>582</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>583</v>
+        <v>553</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>584</v>
+        <v>554</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>586</v>
+        <v>556</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>587</v>
+        <v>557</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>588</v>
+        <v>558</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>589</v>
+        <v>559</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30">
+      <c r="A17" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15">
+      <c r="A18" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15">
+      <c r="A19" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15">
+      <c r="A20" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15">
+      <c r="A21" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15">
+      <c r="A22" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15">
+      <c r="A23" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>571</v>
       </c>
     </row>
   </sheetData>
